--- a/可见性_1118.xlsx
+++ b/可见性_1118.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ethan/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ethan/Mac本地文稿/0-本地项目/GezhiPlatform/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F76428CA-DE7A-2343-9A2C-565C9CFA7201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B411A54B-AB6B-1242-AA29-B4D6637FB2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25660" yWindow="620" windowWidth="25540" windowHeight="26460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="63">
   <si>
     <t>一级项目</t>
   </si>
@@ -260,12 +260,73 @@
     <t>/</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
+  <si>
+    <t>学生手机号 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>民族 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>初中所在区 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>初中学校 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>个人信息
+必填限制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>入学信息
+必填限制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>地址信息
+必填限制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>户籍地址 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住地址 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住地街道 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>居住地居委 必填</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>至少一个限制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>家庭信息
+填写限制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>健康声明
+必填限制</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +359,33 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman Regular"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体-简 常规体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="9"/>
+      <name val="宋体-简"/>
+      <family val="1"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Times New Roman Regular"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -313,7 +401,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -438,13 +526,88 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -481,6 +644,18 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -490,19 +665,76 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -996,7 +1228,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="2" customWidth="1"/>
@@ -1011,10 +1243,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="18">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13" t="s">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1050,16 +1282,16 @@
       <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="16" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="19" thickBot="1">
-      <c r="A2" s="14"/>
-      <c r="B2" s="14"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
       <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
@@ -1093,11 +1325,11 @@
       <c r="M2" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -1127,10 +1359,10 @@
       <c r="J3" s="4">
         <v>1</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="12">
         <v>1</v>
       </c>
       <c r="M3" s="9" t="s">
@@ -1141,7 +1373,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1">
-      <c r="A4" s="13"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
@@ -1151,28 +1383,28 @@
       <c r="D4" s="6">
         <v>1</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="H4" s="6">
         <v>1</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="I4" s="2" t="s">
         <v>48</v>
       </c>
       <c r="J4" s="6">
         <v>1</v>
       </c>
-      <c r="K4" s="16" t="s">
+      <c r="K4" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="L4" s="16">
+      <c r="L4" s="13">
         <v>1</v>
       </c>
       <c r="M4" s="10" t="s">
@@ -1183,7 +1415,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" ht="18" customHeight="1">
-      <c r="A5" s="13"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1193,28 +1425,28 @@
       <c r="D5" s="6">
         <v>1</v>
       </c>
-      <c r="E5" s="17">
+      <c r="E5" s="2">
         <v>0</v>
       </c>
       <c r="F5" s="6">
         <v>1</v>
       </c>
-      <c r="G5" s="17">
+      <c r="G5" s="2">
         <v>1</v>
       </c>
       <c r="H5" s="6">
         <v>1</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="2">
         <v>1</v>
       </c>
       <c r="J5" s="6">
         <v>1</v>
       </c>
-      <c r="K5" s="16">
-        <v>1</v>
-      </c>
-      <c r="L5" s="16">
+      <c r="K5" s="13">
+        <v>1</v>
+      </c>
+      <c r="L5" s="13">
         <v>1</v>
       </c>
       <c r="M5" s="10">
@@ -1226,7 +1458,7 @@
       <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
-      <c r="A6" s="13"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
@@ -1236,28 +1468,28 @@
       <c r="D6" s="6">
         <v>1</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="2">
         <v>0</v>
       </c>
       <c r="F6" s="6">
         <v>1</v>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="6">
         <v>1</v>
       </c>
-      <c r="I6" s="17">
+      <c r="I6" s="2">
         <v>1</v>
       </c>
       <c r="J6" s="6">
         <v>1</v>
       </c>
-      <c r="K6" s="16">
-        <v>1</v>
-      </c>
-      <c r="L6" s="16">
+      <c r="K6" s="13">
+        <v>1</v>
+      </c>
+      <c r="L6" s="13">
         <v>0</v>
       </c>
       <c r="M6" s="10">
@@ -1268,7 +1500,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" ht="18" customHeight="1">
-      <c r="A7" s="13"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1278,28 +1510,28 @@
       <c r="D7" s="6">
         <v>1</v>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="2">
         <v>0</v>
       </c>
       <c r="F7" s="6">
         <v>1</v>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="2">
         <v>1</v>
       </c>
       <c r="H7" s="6">
         <v>1</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="2">
         <v>1</v>
       </c>
       <c r="J7" s="6">
         <v>1</v>
       </c>
-      <c r="K7" s="16">
-        <v>1</v>
-      </c>
-      <c r="L7" s="16">
+      <c r="K7" s="13">
+        <v>1</v>
+      </c>
+      <c r="L7" s="13">
         <v>0</v>
       </c>
       <c r="M7" s="10">
@@ -1311,7 +1543,7 @@
       <c r="O7" s="3"/>
     </row>
     <row r="8" spans="1:15" ht="18" customHeight="1">
-      <c r="A8" s="13"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
@@ -1321,28 +1553,28 @@
       <c r="D8" s="6">
         <v>0</v>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="2">
         <v>0</v>
       </c>
       <c r="F8" s="6">
         <v>1</v>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="6">
         <v>1</v>
       </c>
-      <c r="I8" s="17">
+      <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="6">
         <v>1</v>
       </c>
-      <c r="K8" s="16">
-        <v>0</v>
-      </c>
-      <c r="L8" s="16">
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
         <v>0</v>
       </c>
       <c r="M8" s="10">
@@ -1353,7 +1585,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" ht="18" customHeight="1">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="17" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1365,28 +1597,28 @@
       <c r="D9" s="6">
         <v>0</v>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="2">
         <v>0</v>
       </c>
       <c r="F9" s="6">
         <v>1</v>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="2">
         <v>1</v>
       </c>
       <c r="H9" s="6">
         <v>1</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="2">
         <v>1</v>
       </c>
       <c r="J9" s="6">
         <v>0</v>
       </c>
-      <c r="K9" s="16">
-        <v>0</v>
-      </c>
-      <c r="L9" s="16">
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
         <v>0</v>
       </c>
       <c r="M9" s="10">
@@ -1397,7 +1629,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" ht="18" customHeight="1">
-      <c r="A10" s="13"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
@@ -1407,28 +1639,28 @@
       <c r="D10" s="6">
         <v>0</v>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="2">
         <v>0</v>
       </c>
       <c r="F10" s="6">
         <v>1</v>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="2">
         <v>1</v>
       </c>
       <c r="H10" s="6">
         <v>1</v>
       </c>
-      <c r="I10" s="17">
+      <c r="I10" s="2">
         <v>1</v>
       </c>
       <c r="J10" s="6">
         <v>0</v>
       </c>
-      <c r="K10" s="16">
-        <v>0</v>
-      </c>
-      <c r="L10" s="16">
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
         <v>0</v>
       </c>
       <c r="M10" s="10">
@@ -1439,7 +1671,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1">
-      <c r="A11" s="13"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1449,28 +1681,28 @@
       <c r="D11" s="6">
         <v>0</v>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="2">
         <v>0</v>
       </c>
       <c r="F11" s="6">
         <v>0</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="6">
         <v>0</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="2">
         <v>0</v>
       </c>
       <c r="J11" s="6">
         <v>0</v>
       </c>
-      <c r="K11" s="16">
-        <v>0</v>
-      </c>
-      <c r="L11" s="16">
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
         <v>0</v>
       </c>
       <c r="M11" s="10">
@@ -1481,7 +1713,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" ht="18" customHeight="1">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="17" t="s">
         <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1493,28 +1725,28 @@
       <c r="D12" s="6">
         <v>1</v>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="2">
         <v>0</v>
       </c>
       <c r="F12" s="6">
         <v>1</v>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="2">
         <v>1</v>
       </c>
       <c r="H12" s="6">
         <v>1</v>
       </c>
-      <c r="I12" s="17">
+      <c r="I12" s="2">
         <v>1</v>
       </c>
       <c r="J12" s="6">
         <v>1</v>
       </c>
-      <c r="K12" s="16">
-        <v>0</v>
-      </c>
-      <c r="L12" s="16">
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
         <v>0</v>
       </c>
       <c r="M12" s="10">
@@ -1526,7 +1758,7 @@
       <c r="O12" s="3"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1">
-      <c r="A13" s="13"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1536,28 +1768,28 @@
       <c r="D13" s="6">
         <v>1</v>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="2">
         <v>0</v>
       </c>
       <c r="F13" s="6">
         <v>1</v>
       </c>
-      <c r="G13" s="17">
+      <c r="G13" s="2">
         <v>1</v>
       </c>
       <c r="H13" s="6">
         <v>1</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="2">
         <v>1</v>
       </c>
       <c r="J13" s="6">
         <v>1</v>
       </c>
-      <c r="K13" s="16">
-        <v>0</v>
-      </c>
-      <c r="L13" s="16">
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
         <v>1</v>
       </c>
       <c r="M13" s="10">
@@ -1569,7 +1801,7 @@
       <c r="O13" s="3"/>
     </row>
     <row r="14" spans="1:15" ht="18" customHeight="1">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="17" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1581,28 +1813,28 @@
       <c r="D14" s="6">
         <v>1</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="2">
         <v>0</v>
       </c>
       <c r="F14" s="6">
         <v>1</v>
       </c>
-      <c r="G14" s="17">
+      <c r="G14" s="2">
         <v>1</v>
       </c>
       <c r="H14" s="6">
         <v>1</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="2">
         <v>1</v>
       </c>
       <c r="J14" s="6">
         <v>1</v>
       </c>
-      <c r="K14" s="16">
-        <v>0</v>
-      </c>
-      <c r="L14" s="16">
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
         <v>1</v>
       </c>
       <c r="M14" s="10">
@@ -1614,7 +1846,7 @@
       <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" ht="18" customHeight="1">
-      <c r="A15" s="13"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
@@ -1624,28 +1856,28 @@
       <c r="D15" s="6">
         <v>1</v>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="2">
         <v>0</v>
       </c>
       <c r="F15" s="6">
         <v>1</v>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="2">
         <v>1</v>
       </c>
       <c r="H15" s="6">
         <v>1</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="2">
         <v>1</v>
       </c>
       <c r="J15" s="6">
         <v>1</v>
       </c>
-      <c r="K15" s="16">
-        <v>0</v>
-      </c>
-      <c r="L15" s="16">
+      <c r="K15" s="13">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13">
         <v>1</v>
       </c>
       <c r="M15" s="10">
@@ -1657,7 +1889,7 @@
       <c r="O15" s="3"/>
     </row>
     <row r="16" spans="1:15" ht="18" customHeight="1">
-      <c r="A16" s="13"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="1" t="s">
         <v>26</v>
       </c>
@@ -1667,28 +1899,28 @@
       <c r="D16" s="6">
         <v>1</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="2">
         <v>0</v>
       </c>
       <c r="F16" s="6">
         <v>1</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="2">
         <v>1</v>
       </c>
       <c r="H16" s="6">
         <v>1</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="2">
         <v>1</v>
       </c>
       <c r="J16" s="6">
         <v>0</v>
       </c>
-      <c r="K16" s="16">
-        <v>0</v>
-      </c>
-      <c r="L16" s="16">
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
         <v>0</v>
       </c>
       <c r="M16" s="10">
@@ -1700,7 +1932,7 @@
       <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
-      <c r="A17" s="13"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="1" t="s">
         <v>27</v>
       </c>
@@ -1710,28 +1942,28 @@
       <c r="D17" s="6">
         <v>1</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E17" s="2">
         <v>0</v>
       </c>
       <c r="F17" s="6">
         <v>1</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="2">
         <v>1</v>
       </c>
       <c r="H17" s="6">
         <v>1</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="2">
         <v>1</v>
       </c>
       <c r="J17" s="6">
         <v>1</v>
       </c>
-      <c r="K17" s="16">
-        <v>0</v>
-      </c>
-      <c r="L17" s="16">
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
         <v>1</v>
       </c>
       <c r="M17" s="10">
@@ -1743,7 +1975,7 @@
       <c r="O17" s="3"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1">
-      <c r="A18" s="13"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="1" t="s">
         <v>28</v>
       </c>
@@ -1753,28 +1985,28 @@
       <c r="D18" s="6">
         <v>1</v>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="2">
         <v>0</v>
       </c>
       <c r="F18" s="6">
         <v>1</v>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="2">
         <v>1</v>
       </c>
       <c r="H18" s="6">
         <v>1</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="2">
         <v>1</v>
       </c>
       <c r="J18" s="6">
         <v>1</v>
       </c>
-      <c r="K18" s="16">
-        <v>0</v>
-      </c>
-      <c r="L18" s="16">
+      <c r="K18" s="13">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
         <v>1</v>
       </c>
       <c r="M18" s="10">
@@ -1786,7 +2018,7 @@
       <c r="O18" s="3"/>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
-      <c r="A19" s="13"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="1" t="s">
         <v>29</v>
       </c>
@@ -1796,28 +2028,28 @@
       <c r="D19" s="6">
         <v>1</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="2">
         <v>0</v>
       </c>
       <c r="F19" s="6">
         <v>1</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="2">
         <v>1</v>
       </c>
       <c r="H19" s="6">
         <v>1</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="2">
         <v>1</v>
       </c>
       <c r="J19" s="6">
         <v>0</v>
       </c>
-      <c r="K19" s="16">
-        <v>0</v>
-      </c>
-      <c r="L19" s="16">
+      <c r="K19" s="13">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13">
         <v>0</v>
       </c>
       <c r="M19" s="10">
@@ -1829,7 +2061,7 @@
       <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:15" ht="18" customHeight="1">
-      <c r="A20" s="13"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="1" t="s">
         <v>30</v>
       </c>
@@ -1839,31 +2071,31 @@
       <c r="D20" s="6">
         <v>1</v>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="2">
         <v>0</v>
       </c>
       <c r="F20" s="6">
         <v>1</v>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="15">
         <v>5</v>
       </c>
       <c r="H20" s="6">
         <v>1</v>
       </c>
-      <c r="I20" s="19">
+      <c r="I20" s="15">
         <v>5</v>
       </c>
       <c r="J20" s="6">
         <v>1</v>
       </c>
-      <c r="K20" s="16">
-        <v>0</v>
-      </c>
-      <c r="L20" s="16">
-        <v>0</v>
-      </c>
-      <c r="M20" s="19">
+      <c r="K20" s="13">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="15">
         <v>5</v>
       </c>
       <c r="N20" s="3" t="s">
@@ -1872,7 +2104,7 @@
       <c r="O20" s="3"/>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1">
-      <c r="A21" s="13"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="1" t="s">
         <v>31</v>
       </c>
@@ -1882,31 +2114,31 @@
       <c r="D21" s="6">
         <v>1</v>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="2">
         <v>0</v>
       </c>
       <c r="F21" s="6">
         <v>1</v>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="15">
         <v>5</v>
       </c>
       <c r="H21" s="6">
         <v>1</v>
       </c>
-      <c r="I21" s="19">
+      <c r="I21" s="15">
         <v>5</v>
       </c>
       <c r="J21" s="6">
         <v>1</v>
       </c>
-      <c r="K21" s="16">
-        <v>0</v>
-      </c>
-      <c r="L21" s="16">
-        <v>0</v>
-      </c>
-      <c r="M21" s="19">
+      <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="15">
         <v>5</v>
       </c>
       <c r="N21" s="3" t="s">
@@ -1915,7 +2147,7 @@
       <c r="O21" s="3"/>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1">
-      <c r="A22" s="13"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="1" t="s">
         <v>32</v>
       </c>
@@ -1925,31 +2157,31 @@
       <c r="D22" s="6">
         <v>1</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="2">
         <v>0</v>
       </c>
       <c r="F22" s="6">
         <v>1</v>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="15">
         <v>5</v>
       </c>
       <c r="H22" s="6">
         <v>1</v>
       </c>
-      <c r="I22" s="19">
+      <c r="I22" s="15">
         <v>5</v>
       </c>
       <c r="J22" s="6">
         <v>1</v>
       </c>
-      <c r="K22" s="16">
-        <v>0</v>
-      </c>
-      <c r="L22" s="16">
-        <v>0</v>
-      </c>
-      <c r="M22" s="19">
+      <c r="K22" s="13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="15">
         <v>5</v>
       </c>
       <c r="N22" s="3" t="s">
@@ -1958,7 +2190,7 @@
       <c r="O22" s="3"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="17" t="s">
         <v>33</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1970,31 +2202,31 @@
       <c r="D23" s="6">
         <v>1</v>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="15">
         <v>2</v>
       </c>
       <c r="F23" s="6">
         <v>1</v>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="15">
         <v>5</v>
       </c>
       <c r="H23" s="6">
         <v>0</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="2">
         <v>0</v>
       </c>
       <c r="J23" s="6">
         <v>0</v>
       </c>
-      <c r="K23" s="16">
-        <v>0</v>
-      </c>
-      <c r="L23" s="16">
-        <v>0</v>
-      </c>
-      <c r="M23" s="19">
+      <c r="K23" s="13">
+        <v>0</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="15">
         <v>2</v>
       </c>
       <c r="N23" s="2" t="s">
@@ -2002,7 +2234,7 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="18" customHeight="1">
-      <c r="A24" s="13"/>
+      <c r="A24" s="17"/>
       <c r="B24" s="1" t="s">
         <v>36</v>
       </c>
@@ -2012,31 +2244,31 @@
       <c r="D24" s="6">
         <v>1</v>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="15">
         <v>2</v>
       </c>
       <c r="F24" s="6">
         <v>1</v>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="15">
         <v>5</v>
       </c>
       <c r="H24" s="6">
         <v>0</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="2">
         <v>0</v>
       </c>
       <c r="J24" s="6">
         <v>0</v>
       </c>
-      <c r="K24" s="16">
-        <v>0</v>
-      </c>
-      <c r="L24" s="16">
-        <v>0</v>
-      </c>
-      <c r="M24" s="19">
+      <c r="K24" s="13">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="15">
         <v>2</v>
       </c>
       <c r="N24" s="2" t="s">
@@ -2044,7 +2276,7 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="18" customHeight="1">
-      <c r="A25" s="13"/>
+      <c r="A25" s="17"/>
       <c r="B25" s="1" t="s">
         <v>37</v>
       </c>
@@ -2054,31 +2286,31 @@
       <c r="D25" s="6">
         <v>1</v>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="15">
         <v>2</v>
       </c>
       <c r="F25" s="6">
         <v>1</v>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="15">
         <v>5</v>
       </c>
       <c r="H25" s="6">
         <v>0</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="2">
         <v>0</v>
       </c>
       <c r="J25" s="6">
         <v>0</v>
       </c>
-      <c r="K25" s="16">
-        <v>0</v>
-      </c>
-      <c r="L25" s="16">
-        <v>0</v>
-      </c>
-      <c r="M25" s="19">
+      <c r="K25" s="13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
         <v>2</v>
       </c>
       <c r="N25" s="2" t="s">
@@ -2086,7 +2318,7 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18" customHeight="1" thickBot="1">
-      <c r="A26" s="13"/>
+      <c r="A26" s="17"/>
       <c r="B26" s="1" t="s">
         <v>38</v>
       </c>
@@ -2114,10 +2346,10 @@
       <c r="J26" s="7">
         <v>0</v>
       </c>
-      <c r="K26" s="18" t="s">
+      <c r="K26" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="L26" s="18">
+      <c r="L26" s="13">
         <v>0</v>
       </c>
       <c r="M26" s="11" t="s">
@@ -2127,8 +2359,452 @@
         <v>35</v>
       </c>
     </row>
+    <row r="27" spans="1:15" ht="18" customHeight="1">
+      <c r="A27" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="28">
+        <v>0</v>
+      </c>
+      <c r="D27" s="23">
+        <v>0</v>
+      </c>
+      <c r="E27" s="24"/>
+      <c r="F27" s="23">
+        <v>1</v>
+      </c>
+      <c r="G27" s="24"/>
+      <c r="H27" s="23">
+        <v>1</v>
+      </c>
+      <c r="I27" s="24"/>
+      <c r="J27" s="23">
+        <v>1</v>
+      </c>
+      <c r="K27" s="37"/>
+      <c r="L27" s="28">
+        <v>0</v>
+      </c>
+      <c r="M27" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" ht="18">
+      <c r="A28" s="17"/>
+      <c r="B28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="29"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="34"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="33"/>
+    </row>
+    <row r="29" spans="1:15" ht="18">
+      <c r="A29" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="29"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="25">
+        <v>1</v>
+      </c>
+      <c r="G29" s="26"/>
+      <c r="H29" s="25">
+        <v>1</v>
+      </c>
+      <c r="I29" s="26"/>
+      <c r="J29" s="35">
+        <v>0</v>
+      </c>
+      <c r="K29" s="39"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" ht="18">
+      <c r="A30" s="17"/>
+      <c r="B30" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="29"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="25"/>
+      <c r="K30" s="40"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="22"/>
+    </row>
+    <row r="31" spans="1:15" ht="18" customHeight="1">
+      <c r="A31" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C31" s="29"/>
+      <c r="D31" s="25"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="35">
+        <v>1</v>
+      </c>
+      <c r="G31" s="36"/>
+      <c r="H31" s="35">
+        <v>1</v>
+      </c>
+      <c r="I31" s="36"/>
+      <c r="J31" s="25">
+        <v>0</v>
+      </c>
+      <c r="K31" s="40"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" ht="18">
+      <c r="A32" s="16"/>
+      <c r="B32" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="25"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="25"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="25"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="25"/>
+      <c r="K32" s="40"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="22"/>
+    </row>
+    <row r="33" spans="1:13" ht="18">
+      <c r="A33" s="16"/>
+      <c r="B33" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C33" s="29"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="40"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="22"/>
+    </row>
+    <row r="34" spans="1:13" ht="18">
+      <c r="A34" s="16"/>
+      <c r="B34" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="29"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="25"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="25"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="22"/>
+    </row>
+    <row r="35" spans="1:13" ht="18">
+      <c r="A35" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="29"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="35">
+        <v>1</v>
+      </c>
+      <c r="G35" s="36"/>
+      <c r="H35" s="35">
+        <v>1</v>
+      </c>
+      <c r="I35" s="36"/>
+      <c r="J35" s="25">
+        <v>0</v>
+      </c>
+      <c r="K35" s="40"/>
+      <c r="L35" s="29"/>
+      <c r="M35" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" ht="18">
+      <c r="A36" s="21"/>
+      <c r="B36" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="29"/>
+      <c r="D36" s="25"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="25"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="25"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="25"/>
+      <c r="K36" s="40"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="22"/>
+    </row>
+    <row r="37" spans="1:13" ht="18">
+      <c r="A37" s="21"/>
+      <c r="B37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C37" s="29"/>
+      <c r="D37" s="25"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="25"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="25"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="25"/>
+      <c r="K37" s="40"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="22"/>
+    </row>
+    <row r="38" spans="1:13" ht="18">
+      <c r="A38" s="21"/>
+      <c r="B38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="29"/>
+      <c r="D38" s="25"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="25"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="25"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="25"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="29"/>
+      <c r="M38" s="22"/>
+    </row>
+    <row r="39" spans="1:13" ht="18">
+      <c r="A39" s="21"/>
+      <c r="B39" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" s="29"/>
+      <c r="D39" s="25"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="25"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="25"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="25"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="22"/>
+    </row>
+    <row r="40" spans="1:13" ht="18">
+      <c r="A40" s="21"/>
+      <c r="B40" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C40" s="29"/>
+      <c r="D40" s="25"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="25"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="25"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="25"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="22"/>
+    </row>
+    <row r="41" spans="1:13" ht="18">
+      <c r="A41" s="21"/>
+      <c r="B41" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="29"/>
+      <c r="D41" s="25"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="25"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="25"/>
+      <c r="K41" s="40"/>
+      <c r="L41" s="29"/>
+      <c r="M41" s="22"/>
+    </row>
+    <row r="42" spans="1:13" ht="18">
+      <c r="A42" s="21"/>
+      <c r="B42" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="29"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="25"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="25"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="25"/>
+      <c r="K42" s="40"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="22"/>
+    </row>
+    <row r="43" spans="1:13" ht="18">
+      <c r="A43" s="21"/>
+      <c r="B43" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C43" s="29"/>
+      <c r="D43" s="25"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="25"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="25"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="25"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="22"/>
+    </row>
+    <row r="44" spans="1:13" ht="18">
+      <c r="A44" s="21"/>
+      <c r="B44" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="29"/>
+      <c r="D44" s="25"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="34"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="25"/>
+      <c r="K44" s="40"/>
+      <c r="L44" s="29"/>
+      <c r="M44" s="22"/>
+    </row>
+    <row r="45" spans="1:13" ht="18">
+      <c r="A45" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="29"/>
+      <c r="D45" s="25">
+        <v>1</v>
+      </c>
+      <c r="E45" s="26"/>
+      <c r="F45" s="25">
+        <v>1</v>
+      </c>
+      <c r="G45" s="26"/>
+      <c r="H45" s="35">
+        <v>0</v>
+      </c>
+      <c r="I45" s="36"/>
+      <c r="J45" s="25">
+        <v>0</v>
+      </c>
+      <c r="K45" s="40"/>
+      <c r="L45" s="29"/>
+      <c r="M45" s="22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="18">
+      <c r="A46" s="21"/>
+      <c r="B46" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C46" s="29"/>
+      <c r="D46" s="25"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="25"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="25"/>
+      <c r="I46" s="26"/>
+      <c r="J46" s="25"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="22"/>
+    </row>
+    <row r="47" spans="1:13" ht="19" thickBot="1">
+      <c r="A47" s="21"/>
+      <c r="B47" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="30"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="32"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="32"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="32"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="41"/>
+      <c r="L47" s="30"/>
+      <c r="M47" s="27"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="38">
+    <mergeCell ref="F29:G30"/>
+    <mergeCell ref="H29:I30"/>
+    <mergeCell ref="J29:K30"/>
+    <mergeCell ref="C27:C47"/>
+    <mergeCell ref="D45:E47"/>
+    <mergeCell ref="D27:E44"/>
+    <mergeCell ref="F31:G34"/>
+    <mergeCell ref="F35:G44"/>
+    <mergeCell ref="F45:G47"/>
+    <mergeCell ref="H31:I34"/>
+    <mergeCell ref="H35:I44"/>
+    <mergeCell ref="H45:I47"/>
+    <mergeCell ref="J31:K34"/>
+    <mergeCell ref="J35:K44"/>
+    <mergeCell ref="J45:K47"/>
+    <mergeCell ref="M27:M28"/>
+    <mergeCell ref="F27:G28"/>
+    <mergeCell ref="H27:I28"/>
+    <mergeCell ref="J27:K28"/>
+    <mergeCell ref="L27:L47"/>
+    <mergeCell ref="M29:M30"/>
+    <mergeCell ref="M31:M34"/>
+    <mergeCell ref="M35:M44"/>
+    <mergeCell ref="M45:M47"/>
+    <mergeCell ref="A35:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="A31:A34"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="A12:A13"/>
@@ -2140,7 +2816,7 @@
     <mergeCell ref="A3:A8"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="F2 G1:L2 C1:E2 C3:L1048576 E2:E1048576 K2:K1048576 I2:I1048576 M2:M1048576">
+  <conditionalFormatting sqref="C1:E2 G1:L2 F2 E2:E26 I2:I26 K2:K26 M2:M26 C3:L26 C27:D27 F27 C48:M1048576 F29 J29 D45 F31 F35 F45 H27 H29 H31 H35 H45 J27 J31 J35 J45 M31 L27:M27 M35 M45">
     <cfRule type="cellIs" dxfId="0" priority="45" operator="equal">
       <formula>1</formula>
     </cfRule>
